--- a/htb_machines_UPDATE.xlsx
+++ b/htb_machines_UPDATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS\HTB-EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A511CA0-9FD0-4D8A-A85C-AB0C9DE969EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7EA14D-5760-4D2D-83C3-DB9545A194AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="261">
   <si>
     <t>Nombre</t>
   </si>
@@ -772,6 +772,42 @@
   </si>
   <si>
     <t>https://app.hackthebox.com/machines/support</t>
+  </si>
+  <si>
+    <t>Snapped</t>
+  </si>
+  <si>
+    <t>DevArea</t>
+  </si>
+  <si>
+    <t>Garfield</t>
+  </si>
+  <si>
+    <t>Snapped HackTheBox (Hard)</t>
+  </si>
+  <si>
+    <t>DevArea HackTheBox (Intermediate)</t>
+  </si>
+  <si>
+    <t>Garfield HackTheBox (Hard)</t>
+  </si>
+  <si>
+    <t>ctf, writeup, web, ad, smb, politicas, dc</t>
+  </si>
+  <si>
+    <t>ctf, writeup, web, json, xml, sudo</t>
+  </si>
+  <si>
+    <t>ctf, writeup, web, race-condition, fuzz, crack, bypass, suid</t>
+  </si>
+  <si>
+    <t>https://app.hackthebox.com/machines/snapped</t>
+  </si>
+  <si>
+    <t>https://app.hackthebox.com/machines/devarea</t>
+  </si>
+  <si>
+    <t>https://app.hackthebox.com/machines/garfield</t>
   </si>
 </sst>
 </file>
@@ -901,7 +937,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -936,6 +972,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -3086,37 +3123,91 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="A61" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F61" s="10">
+        <v>46104</v>
+      </c>
+      <c r="G61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F62" s="10">
+        <v>46109</v>
+      </c>
+      <c r="G62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="A63" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F63" s="10">
+        <v>46116</v>
+      </c>
+      <c r="G63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
@@ -3246,10 +3337,13 @@
     <hyperlink ref="H9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="H59" r:id="rId4" xr:uid="{9EA76FCF-3C41-4736-9794-A24657154ABF}"/>
     <hyperlink ref="H60" r:id="rId5" xr:uid="{6760F95E-C528-45A1-828C-ACE1B850C4F1}"/>
+    <hyperlink ref="H61" r:id="rId6" xr:uid="{F78A6991-56E4-43C8-A3E3-627B001177E1}"/>
+    <hyperlink ref="H62" r:id="rId7" xr:uid="{3C2E7681-32CB-4234-9267-36EBCD7AC02B}"/>
+    <hyperlink ref="H63" r:id="rId8" xr:uid="{275F7664-0077-445A-8AEA-E4CB4E6D66EC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>